--- a/introductoryExamples/analysis/3-2-w2--trust.xlsx
+++ b/introductoryExamples/analysis/3-2-w2--trust.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>Time</t>
   </si>
@@ -24,6 +24,12 @@
   </si>
   <si>
     <t>#Rep</t>
+  </si>
+  <si>
+    <t>fTi</t>
+  </si>
+  <si>
+    <t>fTa</t>
   </si>
   <si>
     <t>log4j versions2.0-beta through 2.17.0 are vulnerable</t>
@@ -422,21 +428,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="2.8984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="104.39453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="1.8984375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="1.8984375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="4.40234375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="4.31640625" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="3.40234375" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="4.40234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="2.9296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="111.39453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="1.9296875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="1.9296875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="10" max="10" width="4.4296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="12" max="12" width="4.03125" customWidth="true" bestFit="true"/>
+    <col min="13" max="13" width="3.4296875" customWidth="true" bestFit="true"/>
+    <col min="14" max="14" width="4.4296875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,51 +458,59 @@
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="12">
-        <v>30</v>
-      </c>
-      <c r="F1" s="0"/>
+      <c r="E1" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="2">
+        <v>5</v>
+      </c>
       <c r="G1" t="s" s="12">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H1" s="0"/>
       <c r="I1" t="s" s="12">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J1" s="0"/>
       <c r="K1" t="s" s="12">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L1" s="0"/>
+      <c r="M1" t="s" s="12">
+        <v>37</v>
+      </c>
+      <c r="N1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="0"/>
       <c r="B2" s="0"/>
       <c r="C2" s="0"/>
       <c r="D2" s="0"/>
-      <c r="E2" t="s" s="13">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>32</v>
-      </c>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
       <c r="G2" t="s" s="13">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s" s="13">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s" s="13">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="M2" t="s" s="13">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +518,7 @@
         <v>-1.0</v>
       </c>
       <c r="B3" t="s" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>0.0</v>
@@ -512,11 +526,11 @@
       <c r="D3" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E3" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F3" t="n" s="5">
-        <v>1.0</v>
+      <c r="E3" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F3" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G3" t="n" s="15">
         <v>1.0</v>
@@ -534,6 +548,12 @@
         <v>1.0</v>
       </c>
       <c r="L3" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M3" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="N3" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -542,7 +562,7 @@
         <v>-1.0</v>
       </c>
       <c r="B4" t="s" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>0.0</v>
@@ -550,11 +570,11 @@
       <c r="D4" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E4" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F4" t="n" s="5">
-        <v>1.0</v>
+      <c r="E4" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F4" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G4" t="n" s="15">
         <v>1.0</v>
@@ -572,6 +592,12 @@
         <v>1.0</v>
       </c>
       <c r="L4" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M4" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="N4" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -580,7 +606,7 @@
         <v>-1.0</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>1.0</v>
@@ -588,11 +614,11 @@
       <c r="D5" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E5" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F5" t="n" s="5">
-        <v>1.0</v>
+      <c r="E5" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F5" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G5" t="n" s="15">
         <v>1.0</v>
@@ -610,6 +636,12 @@
         <v>1.0</v>
       </c>
       <c r="L5" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M5" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="N5" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -618,7 +650,7 @@
         <v>1.0</v>
       </c>
       <c r="B6" t="s" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>3.0</v>
@@ -626,28 +658,34 @@
       <c r="D6" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E6" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F6" t="n" s="7">
-        <v>0.0</v>
+      <c r="E6" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F6" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G6" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H6" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H6" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I6" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J6" t="n" s="6">
         <v>-0.5</v>
       </c>
-      <c r="I6" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J6" t="n" s="5">
-        <v>1.0</v>
-      </c>
       <c r="K6" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L6" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M6" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N6" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -656,7 +694,7 @@
         <v>1.0</v>
       </c>
       <c r="B7" t="s" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>7.0</v>
@@ -664,28 +702,34 @@
       <c r="D7" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E7" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F7" t="n" s="5">
-        <v>1.0</v>
+      <c r="E7" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F7" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G7" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H7" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="I7" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="K7" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L7" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M7" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -694,7 +738,7 @@
         <v>3.0</v>
       </c>
       <c r="B8" t="s" s="11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>1.0</v>
@@ -702,11 +746,11 @@
       <c r="D8" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E8" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F8" t="n" s="5">
-        <v>1.0</v>
+      <c r="E8" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F8" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G8" t="n" s="15">
         <v>1.0</v>
@@ -715,7 +759,7 @@
         <v>1.0</v>
       </c>
       <c r="I8" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J8" t="n" s="5">
         <v>1.0</v>
@@ -724,6 +768,12 @@
         <v>0.5</v>
       </c>
       <c r="L8" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M8" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -732,7 +782,7 @@
         <v>5.0</v>
       </c>
       <c r="B9" t="s" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>2.0</v>
@@ -740,28 +790,34 @@
       <c r="D9" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E9" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F9" t="n" s="7">
-        <v>0.0</v>
+      <c r="E9" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F9" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G9" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H9" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H9" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I9" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n" s="6">
         <v>-0.5</v>
       </c>
-      <c r="I9" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J9" t="n" s="5">
-        <v>1.0</v>
-      </c>
       <c r="K9" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L9" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M9" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -770,7 +826,7 @@
         <v>7.0</v>
       </c>
       <c r="B10" t="s" s="11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n" s="0">
         <v>0.0</v>
@@ -778,11 +834,11 @@
       <c r="D10" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E10" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F10" t="n" s="5">
-        <v>1.0</v>
+      <c r="E10" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F10" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G10" t="n" s="15">
         <v>1.0</v>
@@ -791,15 +847,21 @@
         <v>1.0</v>
       </c>
       <c r="I10" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J10" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K10" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L10" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N10" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -808,7 +870,7 @@
         <v>7.0</v>
       </c>
       <c r="B11" t="s" s="11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>0.0</v>
@@ -816,11 +878,11 @@
       <c r="D11" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E11" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F11" t="n" s="5">
-        <v>1.0</v>
+      <c r="E11" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F11" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G11" t="n" s="15">
         <v>1.0</v>
@@ -829,15 +891,21 @@
         <v>1.0</v>
       </c>
       <c r="I11" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J11" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K11" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L11" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M11" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N11" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -846,7 +914,7 @@
         <v>7.0</v>
       </c>
       <c r="B12" t="s" s="11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n" s="0">
         <v>1.0</v>
@@ -854,11 +922,11 @@
       <c r="D12" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E12" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F12" t="n" s="5">
-        <v>1.0</v>
+      <c r="E12" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F12" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G12" t="n" s="15">
         <v>1.0</v>
@@ -867,7 +935,7 @@
         <v>1.0</v>
       </c>
       <c r="I12" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J12" t="n" s="5">
         <v>1.0</v>
@@ -876,6 +944,12 @@
         <v>0.5</v>
       </c>
       <c r="L12" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M12" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N12" t="n" s="5">
         <v>1.0</v>
       </c>
     </row>
@@ -884,7 +958,7 @@
         <v>9.0</v>
       </c>
       <c r="B13" t="s" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n" s="0">
         <v>2.0</v>
@@ -892,28 +966,34 @@
       <c r="D13" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E13" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F13" t="n" s="6">
-        <v>-1.0</v>
+      <c r="E13" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F13" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G13" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H13" t="n" s="6">
         <v>-1.0</v>
       </c>
       <c r="I13" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J13" t="n" s="6">
         <v>-1.0</v>
       </c>
       <c r="K13" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L13" t="n" s="6">
+        <v>-1.0</v>
+      </c>
+      <c r="M13" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N13" t="n" s="6">
         <v>-1.0</v>
       </c>
     </row>
@@ -922,7 +1002,7 @@
         <v>11.0</v>
       </c>
       <c r="B14" t="s" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n" s="0">
         <v>2.0</v>
@@ -930,28 +1010,34 @@
       <c r="D14" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E14" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F14" t="n" s="6">
-        <v>-1.0</v>
+      <c r="E14" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F14" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G14" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H14" t="n" s="6">
         <v>-1.0</v>
       </c>
       <c r="I14" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n" s="6">
+        <v>-1.0</v>
+      </c>
+      <c r="K14" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="L14" t="n" s="6">
         <v>-0.5</v>
       </c>
-      <c r="K14" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L14" t="n" s="6">
+      <c r="M14" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N14" t="n" s="6">
         <v>-1.0</v>
       </c>
     </row>
@@ -960,7 +1046,7 @@
         <v>11.0</v>
       </c>
       <c r="B15" t="s" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n" s="0">
         <v>0.0</v>
@@ -968,28 +1054,34 @@
       <c r="D15" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E15" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F15" t="n" s="5">
-        <v>1.0</v>
+      <c r="E15" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F15" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G15" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H15" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I15" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L15" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M15" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N15" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -998,7 +1090,7 @@
         <v>11.0</v>
       </c>
       <c r="B16" t="s" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n" s="0">
         <v>0.0</v>
@@ -1006,28 +1098,34 @@
       <c r="D16" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E16" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F16" t="n" s="5">
-        <v>1.0</v>
+      <c r="E16" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F16" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G16" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H16" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I16" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L16" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M16" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N16" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1036,7 +1134,7 @@
         <v>15.0</v>
       </c>
       <c r="B17" t="s" s="11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n" s="0">
         <v>0.0</v>
@@ -1044,11 +1142,11 @@
       <c r="D17" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E17" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F17" t="n" s="5">
-        <v>1.0</v>
+      <c r="E17" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F17" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G17" t="n" s="15">
         <v>1.0</v>
@@ -1057,15 +1155,21 @@
         <v>1.0</v>
       </c>
       <c r="I17" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J17" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K17" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L17" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M17" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N17" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1074,7 +1178,7 @@
         <v>15.0</v>
       </c>
       <c r="B18" t="s" s="11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n" s="0">
         <v>0.0</v>
@@ -1082,11 +1186,11 @@
       <c r="D18" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E18" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F18" t="n" s="5">
-        <v>1.0</v>
+      <c r="E18" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F18" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G18" t="n" s="15">
         <v>1.0</v>
@@ -1095,15 +1199,21 @@
         <v>1.0</v>
       </c>
       <c r="I18" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J18" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K18" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L18" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M18" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N18" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1112,7 +1222,7 @@
         <v>17.0</v>
       </c>
       <c r="B19" t="s" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n" s="0">
         <v>0.0</v>
@@ -1120,28 +1230,34 @@
       <c r="D19" t="n" s="0">
         <v>1.0</v>
       </c>
-      <c r="E19" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F19" t="n" s="5">
-        <v>1.0</v>
+      <c r="E19" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F19" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G19" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H19" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="I19" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J19" t="n" s="5">
         <v>0.5714285969734192</v>
       </c>
-      <c r="I19" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J19" t="n" s="5">
-        <v>1.0</v>
-      </c>
       <c r="K19" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L19" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M19" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N19" t="n" s="5">
         <v>0.5714285969734192</v>
       </c>
     </row>
@@ -1150,7 +1266,7 @@
         <v>17.0</v>
       </c>
       <c r="B20" t="s" s="10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20" t="n" s="0">
         <v>1.0</v>
@@ -1158,28 +1274,34 @@
       <c r="D20" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E20" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F20" t="n" s="6">
+      <c r="E20" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F20" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="G20" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="H20" t="n" s="6">
         <v>-1.0</v>
       </c>
-      <c r="G20" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H20" t="n" s="6">
+      <c r="I20" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J20" t="n" s="6">
         <v>-0.5</v>
       </c>
-      <c r="I20" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J20" t="n" s="6">
+      <c r="K20" t="n" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="L20" t="n" s="6">
         <v>-1.0</v>
       </c>
-      <c r="K20" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L20" t="n" s="6">
+      <c r="M20" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N20" t="n" s="6">
         <v>-0.5</v>
       </c>
     </row>
@@ -1188,7 +1310,7 @@
         <v>19.0</v>
       </c>
       <c r="B21" t="s" s="10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n" s="0">
         <v>1.0</v>
@@ -1196,28 +1318,34 @@
       <c r="D21" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E21" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F21" t="n" s="6">
-        <v>-1.0</v>
+      <c r="E21" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F21" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G21" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H21" t="n" s="6">
         <v>-1.0</v>
       </c>
       <c r="I21" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J21" t="n" s="7">
-        <v>0.0</v>
+        <v>0.5</v>
+      </c>
+      <c r="J21" t="n" s="6">
+        <v>-1.0</v>
       </c>
       <c r="K21" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L21" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L21" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="M21" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N21" t="n" s="6">
         <v>-0.5</v>
       </c>
     </row>
@@ -1226,7 +1354,7 @@
         <v>19.0</v>
       </c>
       <c r="B22" t="s" s="10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n" s="0">
         <v>0.0</v>
@@ -1234,28 +1362,34 @@
       <c r="D22" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E22" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F22" t="n" s="5">
-        <v>1.0</v>
+      <c r="E22" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F22" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G22" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H22" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I22" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J22" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K22" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L22" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M22" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N22" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1264,7 +1398,7 @@
         <v>21.0</v>
       </c>
       <c r="B23" t="s" s="11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n" s="0">
         <v>0.0</v>
@@ -1272,11 +1406,11 @@
       <c r="D23" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E23" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F23" t="n" s="5">
-        <v>1.0</v>
+      <c r="E23" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F23" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G23" t="n" s="15">
         <v>1.0</v>
@@ -1285,15 +1419,21 @@
         <v>1.0</v>
       </c>
       <c r="I23" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J23" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K23" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L23" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M23" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N23" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1302,7 +1442,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" t="s" s="10">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C24" t="n" s="0">
         <v>2.0</v>
@@ -1310,28 +1450,34 @@
       <c r="D24" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E24" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F24" t="n" s="7">
-        <v>0.0</v>
+      <c r="E24" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F24" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G24" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="H24" t="n" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H24" t="n" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="I24" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="J24" t="n" s="6">
         <v>-0.5</v>
       </c>
-      <c r="I24" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="J24" t="n" s="5">
-        <v>0.5</v>
-      </c>
       <c r="K24" t="n" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="L24" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="L24" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M24" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N24" t="n" s="7">
         <v>0.0</v>
       </c>
     </row>
@@ -1340,7 +1486,7 @@
         <v>25.0</v>
       </c>
       <c r="B25" t="s" s="11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C25" t="n" s="0">
         <v>0.0</v>
@@ -1348,11 +1494,11 @@
       <c r="D25" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E25" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F25" t="n" s="5">
-        <v>1.0</v>
+      <c r="E25" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F25" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G25" t="n" s="15">
         <v>1.0</v>
@@ -1361,15 +1507,21 @@
         <v>1.0</v>
       </c>
       <c r="I25" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J25" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K25" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L25" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M25" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N25" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1378,7 +1530,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" t="s" s="11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C26" t="n" s="0">
         <v>0.0</v>
@@ -1386,11 +1538,11 @@
       <c r="D26" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E26" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F26" t="n" s="5">
-        <v>1.0</v>
+      <c r="E26" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F26" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G26" t="n" s="15">
         <v>1.0</v>
@@ -1399,15 +1551,21 @@
         <v>1.0</v>
       </c>
       <c r="I26" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="J26" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="K26" t="n" s="15">
         <v>0.5</v>
       </c>
       <c r="L26" t="n" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M26" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N26" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1416,7 +1574,7 @@
         <v>27.0</v>
       </c>
       <c r="B27" t="s" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27" t="n" s="0">
         <v>0.0</v>
@@ -1424,28 +1582,34 @@
       <c r="D27" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E27" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F27" t="n" s="5">
-        <v>1.0</v>
+      <c r="E27" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F27" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G27" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I27" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L27" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M27" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N27" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
@@ -1454,7 +1618,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" t="s" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" t="n" s="0">
         <v>0.0</v>
@@ -1462,41 +1626,49 @@
       <c r="D28" t="n" s="0">
         <v>0.0</v>
       </c>
-      <c r="E28" t="n" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="F28" t="n" s="5">
-        <v>1.0</v>
+      <c r="E28" t="e" s="7">
+        <v>#NUM!</v>
+      </c>
+      <c r="F28" t="e" s="7">
+        <v>#NUM!</v>
       </c>
       <c r="G28" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="H28" t="n" s="5">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="I28" t="n" s="15">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n" s="5">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n" s="15">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L28" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="M28" t="n" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="N28" t="n" s="5">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
